--- a/2.RD_CGE/Input_w-t/240125_Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/240125_Projection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39D7353-79A5-4443-BB36-0BA332728F01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88C32F1-E19C-48CD-BAE7-B284BDEAE84C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="699" activeTab="3" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="699" activeTab="7" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -20,13 +20,14 @@
     <sheet name="GDP_Projection" sheetId="3" r:id="rId5"/>
     <sheet name="TOT_POP_Projection" sheetId="5" r:id="rId6"/>
     <sheet name="g_SDR" sheetId="20" r:id="rId7"/>
-    <sheet name="AEEI" sheetId="11" r:id="rId8"/>
-    <sheet name="TREND" sheetId="18" r:id="rId9"/>
-    <sheet name="CTAX_61" sheetId="17" r:id="rId10"/>
-    <sheet name="CTAX_145" sheetId="13" r:id="rId11"/>
-    <sheet name="CTAX_285" sheetId="14" r:id="rId12"/>
-    <sheet name="CTAX_425" sheetId="15" r:id="rId13"/>
-    <sheet name="CTAX_565" sheetId="16" r:id="rId14"/>
+    <sheet name="AEEI_low" sheetId="22" r:id="rId8"/>
+    <sheet name="AEEI_high" sheetId="11" r:id="rId9"/>
+    <sheet name="TREND" sheetId="18" r:id="rId10"/>
+    <sheet name="CTAX_61" sheetId="17" r:id="rId11"/>
+    <sheet name="CTAX_145" sheetId="13" r:id="rId12"/>
+    <sheet name="CTAX_285" sheetId="14" r:id="rId13"/>
+    <sheet name="CTAX_425" sheetId="15" r:id="rId14"/>
+    <sheet name="CTAX_565" sheetId="16" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">GDP_Projection!$A$1:$CF$18</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="88">
   <si>
     <t>01_KOR</t>
   </si>
@@ -2151,6 +2152,1838 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B93DD5-A57F-41E3-A40A-188EC63D5E77}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="33" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="16">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="16">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="16">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="16">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="16">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="16">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="16">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="16">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="16">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="16">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="16">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="16">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="16">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="16">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="16">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="16">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="16">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="16">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="16">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="16">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="16">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="16">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="16">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="16">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="16">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="16">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="16">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="16">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="16">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="16">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0.97</v>
+      </c>
+      <c r="D2">
+        <v>0.9506</v>
+      </c>
+      <c r="E2">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F2">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G2">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H2">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I2">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J2">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K2">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L2">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M2">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N2">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O2">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P2">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q2">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R2">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S2">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T2">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U2">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V2">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W2">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X2">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y2">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z2">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA2">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB2">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC2">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD2">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE2">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF2">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG2">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1.02</v>
+      </c>
+      <c r="D3">
+        <v>0.99960000000000004</v>
+      </c>
+      <c r="E3">
+        <v>0.97960800000000003</v>
+      </c>
+      <c r="F3">
+        <v>0.96001584000000006</v>
+      </c>
+      <c r="G3">
+        <v>0.94081552320000006</v>
+      </c>
+      <c r="H3">
+        <v>0.92199921273600005</v>
+      </c>
+      <c r="I3">
+        <v>0.90355922848128001</v>
+      </c>
+      <c r="J3">
+        <v>0.88548804391165437</v>
+      </c>
+      <c r="K3">
+        <v>0.8677782830334213</v>
+      </c>
+      <c r="L3">
+        <v>0.85042271737275288</v>
+      </c>
+      <c r="M3">
+        <v>0.83341426302529786</v>
+      </c>
+      <c r="N3">
+        <v>0.81674597776479185</v>
+      </c>
+      <c r="O3">
+        <v>0.80041105820949598</v>
+      </c>
+      <c r="P3">
+        <v>0.78440283704530611</v>
+      </c>
+      <c r="Q3">
+        <v>0.76871478030439999</v>
+      </c>
+      <c r="R3">
+        <v>0.75334048469831194</v>
+      </c>
+      <c r="S3">
+        <v>0.73827367500434571</v>
+      </c>
+      <c r="T3">
+        <v>0.72350820150425876</v>
+      </c>
+      <c r="U3">
+        <v>0.7090380374741736</v>
+      </c>
+      <c r="V3">
+        <v>0.69485727672469011</v>
+      </c>
+      <c r="W3">
+        <v>0.68096013119019627</v>
+      </c>
+      <c r="X3">
+        <v>0.66734092856639238</v>
+      </c>
+      <c r="Y3">
+        <v>0.65399410999506458</v>
+      </c>
+      <c r="Z3">
+        <v>0.64091422779516327</v>
+      </c>
+      <c r="AA3">
+        <v>0.62809594323925999</v>
+      </c>
+      <c r="AB3">
+        <v>0.6155340243744748</v>
+      </c>
+      <c r="AC3">
+        <v>0.60322334388698529</v>
+      </c>
+      <c r="AD3">
+        <v>0.59115887700924563</v>
+      </c>
+      <c r="AE3">
+        <v>0.57933569946906072</v>
+      </c>
+      <c r="AF3">
+        <v>0.56774898547967956</v>
+      </c>
+      <c r="AG3">
+        <v>0.55639400577008602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0.97</v>
+      </c>
+      <c r="D4">
+        <v>0.94574999999999998</v>
+      </c>
+      <c r="E4">
+        <v>0.92210625000000002</v>
+      </c>
+      <c r="F4">
+        <v>0.89905359375000005</v>
+      </c>
+      <c r="G4">
+        <v>0.87657725390625008</v>
+      </c>
+      <c r="H4">
+        <v>0.85466282255859383</v>
+      </c>
+      <c r="I4">
+        <v>0.83329625199462898</v>
+      </c>
+      <c r="J4">
+        <v>0.81246384569476326</v>
+      </c>
+      <c r="K4">
+        <v>0.79215224955239416</v>
+      </c>
+      <c r="L4">
+        <v>0.77234844331358432</v>
+      </c>
+      <c r="M4">
+        <v>0.75303973223074472</v>
+      </c>
+      <c r="N4">
+        <v>0.7342137389249761</v>
+      </c>
+      <c r="O4">
+        <v>0.7158583954518517</v>
+      </c>
+      <c r="P4">
+        <v>0.69796193556555541</v>
+      </c>
+      <c r="Q4">
+        <v>0.68051288717641656</v>
+      </c>
+      <c r="R4">
+        <v>0.6635000649970062</v>
+      </c>
+      <c r="S4">
+        <v>0.64691256337208103</v>
+      </c>
+      <c r="T4">
+        <v>0.63073974928777898</v>
+      </c>
+      <c r="U4">
+        <v>0.61497125555558452</v>
+      </c>
+      <c r="V4">
+        <v>0.59959697416669488</v>
+      </c>
+      <c r="W4">
+        <v>0.58460704981252753</v>
+      </c>
+      <c r="X4">
+        <v>0.56999187356721437</v>
+      </c>
+      <c r="Y4">
+        <v>0.555742076728034</v>
+      </c>
+      <c r="Z4">
+        <v>0.54184852480983314</v>
+      </c>
+      <c r="AA4">
+        <v>0.5283023116895873</v>
+      </c>
+      <c r="AB4">
+        <v>0.5150947538973476</v>
+      </c>
+      <c r="AC4">
+        <v>0.50221738504991387</v>
+      </c>
+      <c r="AD4">
+        <v>0.489661950423666</v>
+      </c>
+      <c r="AE4">
+        <v>0.47742040166307437</v>
+      </c>
+      <c r="AF4">
+        <v>0.46548489162149753</v>
+      </c>
+      <c r="AG4">
+        <v>0.4538477693309601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0.97</v>
+      </c>
+      <c r="D5">
+        <v>0.96514999999999995</v>
+      </c>
+      <c r="E5">
+        <v>0.96032424999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.95552262874999994</v>
+      </c>
+      <c r="G5">
+        <v>0.95074501560624991</v>
+      </c>
+      <c r="H5">
+        <v>0.94599129052821862</v>
+      </c>
+      <c r="I5">
+        <v>0.94126133407557755</v>
+      </c>
+      <c r="J5">
+        <v>0.93655502740519969</v>
+      </c>
+      <c r="K5">
+        <v>0.93187225226817372</v>
+      </c>
+      <c r="L5">
+        <v>0.9272128910068328</v>
+      </c>
+      <c r="M5">
+        <v>0.92257682655179862</v>
+      </c>
+      <c r="N5">
+        <v>0.91796394241903967</v>
+      </c>
+      <c r="O5">
+        <v>0.91337412270694451</v>
+      </c>
+      <c r="P5">
+        <v>0.90880725209340985</v>
+      </c>
+      <c r="Q5">
+        <v>0.90426321583294278</v>
+      </c>
+      <c r="R5">
+        <v>0.89974189975377805</v>
+      </c>
+      <c r="S5">
+        <v>0.8952431902550092</v>
+      </c>
+      <c r="T5">
+        <v>0.89076697430373419</v>
+      </c>
+      <c r="U5">
+        <v>0.88631313943221557</v>
+      </c>
+      <c r="V5">
+        <v>0.88188157373505449</v>
+      </c>
+      <c r="W5">
+        <v>0.87747216586637922</v>
+      </c>
+      <c r="X5">
+        <v>0.87308480503704733</v>
+      </c>
+      <c r="Y5">
+        <v>0.86871938101186208</v>
+      </c>
+      <c r="Z5">
+        <v>0.86437578410680271</v>
+      </c>
+      <c r="AA5">
+        <v>0.86005390518626867</v>
+      </c>
+      <c r="AB5">
+        <v>0.85575363566033735</v>
+      </c>
+      <c r="AC5">
+        <v>0.85147486748203571</v>
+      </c>
+      <c r="AD5">
+        <v>0.84721749314462558</v>
+      </c>
+      <c r="AE5">
+        <v>0.84298140567890245</v>
+      </c>
+      <c r="AF5">
+        <v>0.8387664986505079</v>
+      </c>
+      <c r="AG5">
+        <v>0.83457266615725534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0.97</v>
+      </c>
+      <c r="D6">
+        <v>0.96514999999999995</v>
+      </c>
+      <c r="E6">
+        <v>0.96032424999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.95552262874999994</v>
+      </c>
+      <c r="G6">
+        <v>0.95074501560624991</v>
+      </c>
+      <c r="H6">
+        <v>0.94599129052821862</v>
+      </c>
+      <c r="I6">
+        <v>0.94126133407557755</v>
+      </c>
+      <c r="J6">
+        <v>0.93655502740519969</v>
+      </c>
+      <c r="K6">
+        <v>0.93187225226817372</v>
+      </c>
+      <c r="L6">
+        <v>0.9272128910068328</v>
+      </c>
+      <c r="M6">
+        <v>0.92257682655179862</v>
+      </c>
+      <c r="N6">
+        <v>0.91796394241903967</v>
+      </c>
+      <c r="O6">
+        <v>0.91337412270694451</v>
+      </c>
+      <c r="P6">
+        <v>0.90880725209340985</v>
+      </c>
+      <c r="Q6">
+        <v>0.90426321583294278</v>
+      </c>
+      <c r="R6">
+        <v>0.89974189975377805</v>
+      </c>
+      <c r="S6">
+        <v>0.8952431902550092</v>
+      </c>
+      <c r="T6">
+        <v>0.89076697430373419</v>
+      </c>
+      <c r="U6">
+        <v>0.88631313943221557</v>
+      </c>
+      <c r="V6">
+        <v>0.88188157373505449</v>
+      </c>
+      <c r="W6">
+        <v>0.87747216586637922</v>
+      </c>
+      <c r="X6">
+        <v>0.87308480503704733</v>
+      </c>
+      <c r="Y6">
+        <v>0.86871938101186208</v>
+      </c>
+      <c r="Z6">
+        <v>0.86437578410680271</v>
+      </c>
+      <c r="AA6">
+        <v>0.86005390518626867</v>
+      </c>
+      <c r="AB6">
+        <v>0.85575363566033735</v>
+      </c>
+      <c r="AC6">
+        <v>0.85147486748203571</v>
+      </c>
+      <c r="AD6">
+        <v>0.84721749314462558</v>
+      </c>
+      <c r="AE6">
+        <v>0.84298140567890245</v>
+      </c>
+      <c r="AF6">
+        <v>0.8387664986505079</v>
+      </c>
+      <c r="AG6">
+        <v>0.83457266615725534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0.97</v>
+      </c>
+      <c r="D7">
+        <v>0.96514999999999995</v>
+      </c>
+      <c r="E7">
+        <v>0.96032424999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.95552262874999994</v>
+      </c>
+      <c r="G7">
+        <v>0.95074501560624991</v>
+      </c>
+      <c r="H7">
+        <v>0.94599129052821862</v>
+      </c>
+      <c r="I7">
+        <v>0.94126133407557755</v>
+      </c>
+      <c r="J7">
+        <v>0.93655502740519969</v>
+      </c>
+      <c r="K7">
+        <v>0.93187225226817372</v>
+      </c>
+      <c r="L7">
+        <v>0.9272128910068328</v>
+      </c>
+      <c r="M7">
+        <v>0.92257682655179862</v>
+      </c>
+      <c r="N7">
+        <v>0.91796394241903967</v>
+      </c>
+      <c r="O7">
+        <v>0.91337412270694451</v>
+      </c>
+      <c r="P7">
+        <v>0.90880725209340985</v>
+      </c>
+      <c r="Q7">
+        <v>0.90426321583294278</v>
+      </c>
+      <c r="R7">
+        <v>0.89974189975377805</v>
+      </c>
+      <c r="S7">
+        <v>0.8952431902550092</v>
+      </c>
+      <c r="T7">
+        <v>0.89076697430373419</v>
+      </c>
+      <c r="U7">
+        <v>0.88631313943221557</v>
+      </c>
+      <c r="V7">
+        <v>0.88188157373505449</v>
+      </c>
+      <c r="W7">
+        <v>0.87747216586637922</v>
+      </c>
+      <c r="X7">
+        <v>0.87308480503704733</v>
+      </c>
+      <c r="Y7">
+        <v>0.86871938101186208</v>
+      </c>
+      <c r="Z7">
+        <v>0.86437578410680271</v>
+      </c>
+      <c r="AA7">
+        <v>0.86005390518626867</v>
+      </c>
+      <c r="AB7">
+        <v>0.85575363566033735</v>
+      </c>
+      <c r="AC7">
+        <v>0.85147486748203571</v>
+      </c>
+      <c r="AD7">
+        <v>0.84721749314462558</v>
+      </c>
+      <c r="AE7">
+        <v>0.84298140567890245</v>
+      </c>
+      <c r="AF7">
+        <v>0.8387664986505079</v>
+      </c>
+      <c r="AG7">
+        <v>0.83457266615725534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0.97</v>
+      </c>
+      <c r="D8">
+        <v>0.9506</v>
+      </c>
+      <c r="E8">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F8">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G8">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H8">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I8">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J8">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K8">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L8">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M8">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N8">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O8">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P8">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q8">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R8">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S8">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T8">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U8">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V8">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W8">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X8">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y8">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z8">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA8">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB8">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC8">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD8">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE8">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF8">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG8">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0.97</v>
+      </c>
+      <c r="D9">
+        <v>0.96029999999999993</v>
+      </c>
+      <c r="E9">
+        <v>0.9506969999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.9411900299999999</v>
+      </c>
+      <c r="G9">
+        <v>0.93177812969999985</v>
+      </c>
+      <c r="H9">
+        <v>0.92246034840299984</v>
+      </c>
+      <c r="I9">
+        <v>0.91323574491896986</v>
+      </c>
+      <c r="J9">
+        <v>0.90410338746978014</v>
+      </c>
+      <c r="K9">
+        <v>0.89506235359508235</v>
+      </c>
+      <c r="L9">
+        <v>0.88611173005913157</v>
+      </c>
+      <c r="M9">
+        <v>0.87725061275854022</v>
+      </c>
+      <c r="N9">
+        <v>0.86847810663095482</v>
+      </c>
+      <c r="O9">
+        <v>0.85979332556464527</v>
+      </c>
+      <c r="P9">
+        <v>0.85119539230899877</v>
+      </c>
+      <c r="Q9">
+        <v>0.84268343838590876</v>
+      </c>
+      <c r="R9">
+        <v>0.83425660400204971</v>
+      </c>
+      <c r="S9">
+        <v>0.82591403796202922</v>
+      </c>
+      <c r="T9">
+        <v>0.81765489758240895</v>
+      </c>
+      <c r="U9">
+        <v>0.80947834860658485</v>
+      </c>
+      <c r="V9">
+        <v>0.801383565120519</v>
+      </c>
+      <c r="W9">
+        <v>0.79336972946931383</v>
+      </c>
+      <c r="X9">
+        <v>0.78543603217462066</v>
+      </c>
+      <c r="Y9">
+        <v>0.77758167185287441</v>
+      </c>
+      <c r="Z9">
+        <v>0.76980585513434563</v>
+      </c>
+      <c r="AA9">
+        <v>0.76210779658300221</v>
+      </c>
+      <c r="AB9">
+        <v>0.7544867186171722</v>
+      </c>
+      <c r="AC9">
+        <v>0.74694185143100045</v>
+      </c>
+      <c r="AD9">
+        <v>0.7394724329166904</v>
+      </c>
+      <c r="AE9">
+        <v>0.73207770858752352</v>
+      </c>
+      <c r="AF9">
+        <v>0.72475693150164833</v>
+      </c>
+      <c r="AG9">
+        <v>0.71750936218663186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0.97</v>
+      </c>
+      <c r="D10">
+        <v>0.94089999999999996</v>
+      </c>
+      <c r="E10">
+        <v>0.91737749999999996</v>
+      </c>
+      <c r="F10">
+        <v>0.89444306249999994</v>
+      </c>
+      <c r="G10">
+        <v>0.87208198593749997</v>
+      </c>
+      <c r="H10">
+        <v>0.85027993628906251</v>
+      </c>
+      <c r="I10">
+        <v>0.8290229378818359</v>
+      </c>
+      <c r="J10">
+        <v>0.80829736443478994</v>
+      </c>
+      <c r="K10">
+        <v>0.78808993032392016</v>
+      </c>
+      <c r="L10">
+        <v>0.7683876820658222</v>
+      </c>
+      <c r="M10">
+        <v>0.74917799001417662</v>
+      </c>
+      <c r="N10">
+        <v>0.72670265031375136</v>
+      </c>
+      <c r="O10">
+        <v>0.7049015708043388</v>
+      </c>
+      <c r="P10">
+        <v>0.68375452368020861</v>
+      </c>
+      <c r="Q10">
+        <v>0.66324188796980232</v>
+      </c>
+      <c r="R10">
+        <v>0.64334463133070829</v>
+      </c>
+      <c r="S10">
+        <v>0.62404429239078707</v>
+      </c>
+      <c r="T10">
+        <v>0.60532296361906346</v>
+      </c>
+      <c r="U10">
+        <v>0.58716327471049157</v>
+      </c>
+      <c r="V10">
+        <v>0.56954837646917678</v>
+      </c>
+      <c r="W10">
+        <v>0.55246192517510151</v>
+      </c>
+      <c r="X10">
+        <v>0.53588806741984851</v>
+      </c>
+      <c r="Y10">
+        <v>0.519811425397253</v>
+      </c>
+      <c r="Z10">
+        <v>0.50421708263533538</v>
+      </c>
+      <c r="AA10">
+        <v>0.48909057015627533</v>
+      </c>
+      <c r="AB10">
+        <v>0.47441785305158707</v>
+      </c>
+      <c r="AC10">
+        <v>0.46018531746003943</v>
+      </c>
+      <c r="AD10">
+        <v>0.44637975793623824</v>
+      </c>
+      <c r="AE10">
+        <v>0.43298836519815109</v>
+      </c>
+      <c r="AF10">
+        <v>0.41999871424220658</v>
+      </c>
+      <c r="AG10">
+        <v>0.40739875281494037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0.97</v>
+      </c>
+      <c r="D11">
+        <v>0.96514999999999995</v>
+      </c>
+      <c r="E11">
+        <v>0.96032424999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.95552262874999994</v>
+      </c>
+      <c r="G11">
+        <v>0.95074501560624991</v>
+      </c>
+      <c r="H11">
+        <v>0.94599129052821862</v>
+      </c>
+      <c r="I11">
+        <v>0.94126133407557755</v>
+      </c>
+      <c r="J11">
+        <v>0.93655502740519969</v>
+      </c>
+      <c r="K11">
+        <v>0.93187225226817372</v>
+      </c>
+      <c r="L11">
+        <v>0.9272128910068328</v>
+      </c>
+      <c r="M11">
+        <v>0.92257682655179862</v>
+      </c>
+      <c r="N11">
+        <v>0.91796394241903967</v>
+      </c>
+      <c r="O11">
+        <v>0.91337412270694451</v>
+      </c>
+      <c r="P11">
+        <v>0.90880725209340985</v>
+      </c>
+      <c r="Q11">
+        <v>0.90426321583294278</v>
+      </c>
+      <c r="R11">
+        <v>0.89974189975377805</v>
+      </c>
+      <c r="S11">
+        <v>0.8952431902550092</v>
+      </c>
+      <c r="T11">
+        <v>0.89076697430373419</v>
+      </c>
+      <c r="U11">
+        <v>0.88631313943221557</v>
+      </c>
+      <c r="V11">
+        <v>0.88188157373505449</v>
+      </c>
+      <c r="W11">
+        <v>0.87747216586637922</v>
+      </c>
+      <c r="X11">
+        <v>0.87308480503704733</v>
+      </c>
+      <c r="Y11">
+        <v>0.86871938101186208</v>
+      </c>
+      <c r="Z11">
+        <v>0.86437578410680271</v>
+      </c>
+      <c r="AA11">
+        <v>0.86005390518626867</v>
+      </c>
+      <c r="AB11">
+        <v>0.85575363566033735</v>
+      </c>
+      <c r="AC11">
+        <v>0.85147486748203571</v>
+      </c>
+      <c r="AD11">
+        <v>0.84721749314462558</v>
+      </c>
+      <c r="AE11">
+        <v>0.84298140567890245</v>
+      </c>
+      <c r="AF11">
+        <v>0.8387664986505079</v>
+      </c>
+      <c r="AG11">
+        <v>0.83457266615725534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0.97</v>
+      </c>
+      <c r="D12">
+        <v>0.9506</v>
+      </c>
+      <c r="E12">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F12">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G12">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H12">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I12">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J12">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K12">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L12">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M12">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N12">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O12">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P12">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q12">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R12">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S12">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T12">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U12">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V12">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W12">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X12">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y12">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z12">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA12">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB12">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC12">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD12">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE12">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF12">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG12">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0.97</v>
+      </c>
+      <c r="D13">
+        <v>0.9506</v>
+      </c>
+      <c r="E13">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F13">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G13">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H13">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I13">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J13">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K13">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L13">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M13">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N13">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O13">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P13">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q13">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R13">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S13">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T13">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U13">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V13">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W13">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X13">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y13">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z13">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA13">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB13">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC13">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD13">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE13">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF13">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG13">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0.97</v>
+      </c>
+      <c r="D14">
+        <v>0.96029999999999993</v>
+      </c>
+      <c r="E14">
+        <v>0.9506969999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.9411900299999999</v>
+      </c>
+      <c r="G14">
+        <v>0.93177812969999985</v>
+      </c>
+      <c r="H14">
+        <v>0.92246034840299984</v>
+      </c>
+      <c r="I14">
+        <v>0.91323574491896986</v>
+      </c>
+      <c r="J14">
+        <v>0.90410338746978014</v>
+      </c>
+      <c r="K14">
+        <v>0.89506235359508235</v>
+      </c>
+      <c r="L14">
+        <v>0.88611173005913157</v>
+      </c>
+      <c r="M14">
+        <v>0.87725061275854022</v>
+      </c>
+      <c r="N14">
+        <v>0.86847810663095482</v>
+      </c>
+      <c r="O14">
+        <v>0.85979332556464527</v>
+      </c>
+      <c r="P14">
+        <v>0.85119539230899877</v>
+      </c>
+      <c r="Q14">
+        <v>0.84268343838590876</v>
+      </c>
+      <c r="R14">
+        <v>0.83425660400204971</v>
+      </c>
+      <c r="S14">
+        <v>0.82591403796202922</v>
+      </c>
+      <c r="T14">
+        <v>0.81765489758240895</v>
+      </c>
+      <c r="U14">
+        <v>0.80947834860658485</v>
+      </c>
+      <c r="V14">
+        <v>0.801383565120519</v>
+      </c>
+      <c r="W14">
+        <v>0.79336972946931383</v>
+      </c>
+      <c r="X14">
+        <v>0.78543603217462066</v>
+      </c>
+      <c r="Y14">
+        <v>0.77758167185287441</v>
+      </c>
+      <c r="Z14">
+        <v>0.76980585513434563</v>
+      </c>
+      <c r="AA14">
+        <v>0.76210779658300221</v>
+      </c>
+      <c r="AB14">
+        <v>0.7544867186171722</v>
+      </c>
+      <c r="AC14">
+        <v>0.74694185143100045</v>
+      </c>
+      <c r="AD14">
+        <v>0.7394724329166904</v>
+      </c>
+      <c r="AE14">
+        <v>0.73207770858752352</v>
+      </c>
+      <c r="AF14">
+        <v>0.72475693150164833</v>
+      </c>
+      <c r="AG14">
+        <v>0.71750936218663186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0.97</v>
+      </c>
+      <c r="D15">
+        <v>0.9506</v>
+      </c>
+      <c r="E15">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F15">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G15">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H15">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I15">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J15">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K15">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L15">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M15">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N15">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O15">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P15">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q15">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R15">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S15">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T15">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U15">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V15">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W15">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X15">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y15">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z15">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA15">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB15">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC15">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD15">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE15">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF15">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG15">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>0.97</v>
+      </c>
+      <c r="D16">
+        <v>0.95545000000000002</v>
+      </c>
+      <c r="E16">
+        <v>0.94111825000000005</v>
+      </c>
+      <c r="F16">
+        <v>0.92700147625000007</v>
+      </c>
+      <c r="G16">
+        <v>0.91309645410625007</v>
+      </c>
+      <c r="H16">
+        <v>0.8994000072946563</v>
+      </c>
+      <c r="I16">
+        <v>0.88590900718523646</v>
+      </c>
+      <c r="J16">
+        <v>0.87262037207745791</v>
+      </c>
+      <c r="K16">
+        <v>0.85953106649629607</v>
+      </c>
+      <c r="L16">
+        <v>0.84663810049885158</v>
+      </c>
+      <c r="M16">
+        <v>0.83393852899136878</v>
+      </c>
+      <c r="N16">
+        <v>0.82142945105649823</v>
+      </c>
+      <c r="O16">
+        <v>0.80910800929065074</v>
+      </c>
+      <c r="P16">
+        <v>0.79697138915129095</v>
+      </c>
+      <c r="Q16">
+        <v>0.78501681831402159</v>
+      </c>
+      <c r="R16">
+        <v>0.77324156603931127</v>
+      </c>
+      <c r="S16">
+        <v>0.76164294254872156</v>
+      </c>
+      <c r="T16">
+        <v>0.7502182984104907</v>
+      </c>
+      <c r="U16">
+        <v>0.73896502393433339</v>
+      </c>
+      <c r="V16">
+        <v>0.72788054857531836</v>
+      </c>
+      <c r="W16">
+        <v>0.7169623403466886</v>
+      </c>
+      <c r="X16">
+        <v>0.70620790524148824</v>
+      </c>
+      <c r="Y16">
+        <v>0.69561478666286591</v>
+      </c>
+      <c r="Z16">
+        <v>0.68518056486292289</v>
+      </c>
+      <c r="AA16">
+        <v>0.67490285638997904</v>
+      </c>
+      <c r="AB16">
+        <v>0.66477931354412934</v>
+      </c>
+      <c r="AC16">
+        <v>0.65480762384096736</v>
+      </c>
+      <c r="AD16">
+        <v>0.64498550948335287</v>
+      </c>
+      <c r="AE16">
+        <v>0.63531072684110257</v>
+      </c>
+      <c r="AF16">
+        <v>0.62578106593848604</v>
+      </c>
+      <c r="AG16">
+        <v>0.61639434994940878</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>0.97</v>
+      </c>
+      <c r="D17">
+        <v>0.9506</v>
+      </c>
+      <c r="E17">
+        <v>0.93158799999999997</v>
+      </c>
+      <c r="F17">
+        <v>0.91295623999999997</v>
+      </c>
+      <c r="G17">
+        <v>0.89469711519999995</v>
+      </c>
+      <c r="H17">
+        <v>0.87680317289599996</v>
+      </c>
+      <c r="I17">
+        <v>0.85926710943807993</v>
+      </c>
+      <c r="J17">
+        <v>0.84208176724931838</v>
+      </c>
+      <c r="K17">
+        <v>0.82524013190433199</v>
+      </c>
+      <c r="L17">
+        <v>0.80873532926624536</v>
+      </c>
+      <c r="M17">
+        <v>0.79256062268092042</v>
+      </c>
+      <c r="N17">
+        <v>0.776709410227302</v>
+      </c>
+      <c r="O17">
+        <v>0.761175222022756</v>
+      </c>
+      <c r="P17">
+        <v>0.74595171758230083</v>
+      </c>
+      <c r="Q17">
+        <v>0.73103268323065485</v>
+      </c>
+      <c r="R17">
+        <v>0.71641202956604177</v>
+      </c>
+      <c r="S17">
+        <v>0.7020837889747209</v>
+      </c>
+      <c r="T17">
+        <v>0.68804211319522646</v>
+      </c>
+      <c r="U17">
+        <v>0.67428127093132195</v>
+      </c>
+      <c r="V17">
+        <v>0.66079564551269554</v>
+      </c>
+      <c r="W17">
+        <v>0.64757973260244162</v>
+      </c>
+      <c r="X17">
+        <v>0.63462813795039275</v>
+      </c>
+      <c r="Y17">
+        <v>0.62193557519138487</v>
+      </c>
+      <c r="Z17">
+        <v>0.60949686368755718</v>
+      </c>
+      <c r="AA17">
+        <v>0.59730692641380601</v>
+      </c>
+      <c r="AB17">
+        <v>0.58536078788552992</v>
+      </c>
+      <c r="AC17">
+        <v>0.57365357212781931</v>
+      </c>
+      <c r="AD17">
+        <v>0.56218050068526293</v>
+      </c>
+      <c r="AE17">
+        <v>0.55093689067155771</v>
+      </c>
+      <c r="AF17">
+        <v>0.53991815285812661</v>
+      </c>
+      <c r="AG17">
+        <v>0.52911978980096408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0.97</v>
+      </c>
+      <c r="D18">
+        <v>0.94574999999999998</v>
+      </c>
+      <c r="E18">
+        <v>0.92210625000000002</v>
+      </c>
+      <c r="F18">
+        <v>0.89905359375000005</v>
+      </c>
+      <c r="G18">
+        <v>0.87657725390625008</v>
+      </c>
+      <c r="H18">
+        <v>0.85466282255859383</v>
+      </c>
+      <c r="I18">
+        <v>0.83329625199462898</v>
+      </c>
+      <c r="J18">
+        <v>0.81246384569476326</v>
+      </c>
+      <c r="K18">
+        <v>0.79215224955239416</v>
+      </c>
+      <c r="L18">
+        <v>0.77234844331358432</v>
+      </c>
+      <c r="M18">
+        <v>0.75303973223074472</v>
+      </c>
+      <c r="N18">
+        <v>0.7342137389249761</v>
+      </c>
+      <c r="O18">
+        <v>0.7158583954518517</v>
+      </c>
+      <c r="P18">
+        <v>0.69796193556555541</v>
+      </c>
+      <c r="Q18">
+        <v>0.68051288717641656</v>
+      </c>
+      <c r="R18">
+        <v>0.6635000649970062</v>
+      </c>
+      <c r="S18">
+        <v>0.64691256337208103</v>
+      </c>
+      <c r="T18">
+        <v>0.63073974928777898</v>
+      </c>
+      <c r="U18">
+        <v>0.61497125555558452</v>
+      </c>
+      <c r="V18">
+        <v>0.59959697416669488</v>
+      </c>
+      <c r="W18">
+        <v>0.58460704981252753</v>
+      </c>
+      <c r="X18">
+        <v>0.56999187356721437</v>
+      </c>
+      <c r="Y18">
+        <v>0.555742076728034</v>
+      </c>
+      <c r="Z18">
+        <v>0.54184852480983314</v>
+      </c>
+      <c r="AA18">
+        <v>0.5283023116895873</v>
+      </c>
+      <c r="AB18">
+        <v>0.5150947538973476</v>
+      </c>
+      <c r="AC18">
+        <v>0.50221738504991387</v>
+      </c>
+      <c r="AD18">
+        <v>0.489661950423666</v>
+      </c>
+      <c r="AE18">
+        <v>0.47742040166307437</v>
+      </c>
+      <c r="AF18">
+        <v>0.46548489162149753</v>
+      </c>
+      <c r="AG18">
+        <v>0.4538477693309601</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6AC21A-7770-4760-8D5B-5F2CE7B41329}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4452,7 +6285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98116DE7-D39F-483D-A3D2-93FE4B254E46}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6754,7 +8587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F0BF70-BEB3-4C23-BA28-705EDE33B68E}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9056,7 +10889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B36736F-CC09-489B-B698-2F45B1A52627}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11358,7 +13191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B12D2D-5736-4639-9315-A9C245758862}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -39142,6 +40975,2359 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D21ED7-00FD-4715-8862-C6199AA10775}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="16">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="16">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="16">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="16">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="16">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="16">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="16">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="16">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="16">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="16">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="16">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="16">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="16">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="16">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="16">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="16">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="16">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="16">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="16">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="16">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="16">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="16">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="16">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="16">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="16">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="16">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="16">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="16">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="16">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="16">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17">
+        <f>B2-B2*0.005</f>
+        <v>0.995</v>
+      </c>
+      <c r="D2" s="17">
+        <f t="shared" ref="D2:AG10" si="0">C2-C2*0.005</f>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG2" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17">
+        <f t="shared" ref="C3:R18" si="1">B3-B3*0.005</f>
+        <v>0.995</v>
+      </c>
+      <c r="D3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R3" s="17">
+        <f t="shared" si="1"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>1</v>
+      </c>
+      <c r="C4" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17">
+        <v>1</v>
+      </c>
+      <c r="C5" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="17">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="17">
+        <v>1</v>
+      </c>
+      <c r="C8" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="17">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="17">
+        <v>1</v>
+      </c>
+      <c r="C10" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="17">
+        <v>1</v>
+      </c>
+      <c r="C11" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D11" s="17">
+        <f t="shared" ref="D11:AG18" si="2">C11-C11*0.005</f>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="17">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG12" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17">
+        <v>1</v>
+      </c>
+      <c r="C13" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG13" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17">
+        <v>1</v>
+      </c>
+      <c r="C14" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="17">
+        <v>1</v>
+      </c>
+      <c r="C15" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17">
+        <v>1</v>
+      </c>
+      <c r="C16" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG16" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG17" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="17">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17">
+        <f t="shared" si="1"/>
+        <v>0.995</v>
+      </c>
+      <c r="D18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.99002500000000004</v>
+      </c>
+      <c r="E18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98507487500000002</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.98014950062500006</v>
+      </c>
+      <c r="G18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97524875312187509</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.97037250935626573</v>
+      </c>
+      <c r="I18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96552064680948435</v>
+      </c>
+      <c r="J18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.96069304357543694</v>
+      </c>
+      <c r="K18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95588957835755972</v>
+      </c>
+      <c r="L18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.95111013046577197</v>
+      </c>
+      <c r="M18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94635457981344306</v>
+      </c>
+      <c r="N18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.94162280691437583</v>
+      </c>
+      <c r="O18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.936914692879804</v>
+      </c>
+      <c r="P18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.93223011941540501</v>
+      </c>
+      <c r="Q18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92756896881832795</v>
+      </c>
+      <c r="R18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.92293112397423627</v>
+      </c>
+      <c r="S18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91831646835436509</v>
+      </c>
+      <c r="T18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.91372488601259327</v>
+      </c>
+      <c r="U18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90915626158253027</v>
+      </c>
+      <c r="V18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90461048027461766</v>
+      </c>
+      <c r="W18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90008742787324458</v>
+      </c>
+      <c r="X18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89558699073387837</v>
+      </c>
+      <c r="Y18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.89110905578020894</v>
+      </c>
+      <c r="Z18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88665351050130792</v>
+      </c>
+      <c r="AA18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.88222024294880141</v>
+      </c>
+      <c r="AB18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87780914173405744</v>
+      </c>
+      <c r="AC18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.87342009602538717</v>
+      </c>
+      <c r="AD18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86905299554526028</v>
+      </c>
+      <c r="AE18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86470773056753403</v>
+      </c>
+      <c r="AF18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86038419191469639</v>
+      </c>
+      <c r="AG18" s="17">
+        <f t="shared" si="2"/>
+        <v>0.8560822709551229</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501500B2-4CAD-466B-92A4-DF3AC339BC12}">
   <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -39256,128 +43442,128 @@
         <v>1</v>
       </c>
       <c r="C2" s="17">
-        <f>B2-B2*0.02</f>
-        <v>0.98</v>
+        <f>B2-B2*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D2" s="17">
-        <f t="shared" ref="D2:AG2" si="0">C2-C2*0.02</f>
-        <v>0.96040000000000003</v>
+        <f t="shared" ref="D2:AG2" si="0">C2-C2*0.01</f>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E2" s="17">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F2" s="17">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H2" s="17">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I2" s="17">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J2" s="17">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K2" s="17">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L2" s="17">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M2" s="17">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N2" s="17">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O2" s="17">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P2" s="17">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q2" s="17">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R2" s="17">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S2" s="17">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T2" s="17">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U2" s="17">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V2" s="17">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W2" s="17">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X2" s="17">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y2" s="17">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z2" s="17">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA2" s="17">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB2" s="17">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC2" s="17">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD2" s="17">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE2" s="17">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF2" s="17">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG2" s="17">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
@@ -39388,128 +43574,128 @@
         <v>1</v>
       </c>
       <c r="C3" s="17">
-        <f t="shared" ref="C3:AG3" si="1">B3-B3*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C3:AG3" si="1">B3-B3*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D3" s="17">
         <f t="shared" si="1"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E3" s="17">
         <f t="shared" si="1"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" si="1"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="1"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="1"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J3" s="17">
         <f t="shared" si="1"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K3" s="17">
         <f t="shared" si="1"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L3" s="17">
         <f t="shared" si="1"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M3" s="17">
         <f t="shared" si="1"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N3" s="17">
         <f t="shared" si="1"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O3" s="17">
         <f t="shared" si="1"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P3" s="17">
         <f t="shared" si="1"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q3" s="17">
         <f t="shared" si="1"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R3" s="17">
         <f t="shared" si="1"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S3" s="17">
         <f t="shared" si="1"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T3" s="17">
         <f t="shared" si="1"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U3" s="17">
         <f t="shared" si="1"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V3" s="17">
         <f t="shared" si="1"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W3" s="17">
         <f t="shared" si="1"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X3" s="17">
         <f t="shared" si="1"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y3" s="17">
         <f t="shared" si="1"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z3" s="17">
         <f t="shared" si="1"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA3" s="17">
         <f t="shared" si="1"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB3" s="17">
         <f t="shared" si="1"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC3" s="17">
         <f t="shared" si="1"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD3" s="17">
         <f t="shared" si="1"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE3" s="17">
         <f t="shared" si="1"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF3" s="17">
         <f t="shared" si="1"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG3" s="17">
         <f t="shared" si="1"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -39520,128 +43706,128 @@
         <v>1</v>
       </c>
       <c r="C4" s="17">
-        <f t="shared" ref="C4:AG4" si="2">B4-B4*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C4:AG4" si="2">B4-B4*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D4" s="17">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E4" s="17">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J4" s="17">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K4" s="17">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L4" s="17">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M4" s="17">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N4" s="17">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O4" s="17">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P4" s="17">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q4" s="17">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R4" s="17">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S4" s="17">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T4" s="17">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U4" s="17">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V4" s="17">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W4" s="17">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X4" s="17">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y4" s="17">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z4" s="17">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA4" s="17">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB4" s="17">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC4" s="17">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD4" s="17">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE4" s="17">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF4" s="17">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG4" s="17">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -39652,128 +43838,128 @@
         <v>1</v>
       </c>
       <c r="C5" s="17">
-        <f t="shared" ref="C5:AG5" si="3">B5-B5*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C5:AG5" si="3">B5-B5*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D5" s="17">
         <f t="shared" si="3"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E5" s="17">
         <f t="shared" si="3"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="3"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="3"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="3"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="3"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J5" s="17">
         <f t="shared" si="3"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K5" s="17">
         <f t="shared" si="3"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L5" s="17">
         <f t="shared" si="3"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M5" s="17">
         <f t="shared" si="3"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N5" s="17">
         <f t="shared" si="3"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O5" s="17">
         <f t="shared" si="3"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P5" s="17">
         <f t="shared" si="3"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q5" s="17">
         <f t="shared" si="3"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R5" s="17">
         <f t="shared" si="3"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S5" s="17">
         <f t="shared" si="3"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T5" s="17">
         <f t="shared" si="3"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U5" s="17">
         <f t="shared" si="3"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V5" s="17">
         <f t="shared" si="3"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W5" s="17">
         <f t="shared" si="3"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X5" s="17">
         <f t="shared" si="3"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y5" s="17">
         <f t="shared" si="3"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z5" s="17">
         <f t="shared" si="3"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA5" s="17">
         <f t="shared" si="3"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB5" s="17">
         <f t="shared" si="3"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC5" s="17">
         <f t="shared" si="3"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD5" s="17">
         <f t="shared" si="3"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE5" s="17">
         <f t="shared" si="3"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF5" s="17">
         <f t="shared" si="3"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG5" s="17">
         <f t="shared" si="3"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -39784,128 +43970,128 @@
         <v>1</v>
       </c>
       <c r="C6" s="17">
-        <f t="shared" ref="C6:AG6" si="4">B6-B6*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C6:AG6" si="4">B6-B6*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D6" s="17">
         <f t="shared" si="4"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E6" s="17">
         <f t="shared" si="4"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="4"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="4"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="4"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="4"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J6" s="17">
         <f t="shared" si="4"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K6" s="17">
         <f t="shared" si="4"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L6" s="17">
         <f t="shared" si="4"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M6" s="17">
         <f t="shared" si="4"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N6" s="17">
         <f t="shared" si="4"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O6" s="17">
         <f t="shared" si="4"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P6" s="17">
         <f t="shared" si="4"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q6" s="17">
         <f t="shared" si="4"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R6" s="17">
         <f t="shared" si="4"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S6" s="17">
         <f t="shared" si="4"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T6" s="17">
         <f t="shared" si="4"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U6" s="17">
         <f t="shared" si="4"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V6" s="17">
         <f t="shared" si="4"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W6" s="17">
         <f t="shared" si="4"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X6" s="17">
         <f t="shared" si="4"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y6" s="17">
         <f t="shared" si="4"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z6" s="17">
         <f t="shared" si="4"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA6" s="17">
         <f t="shared" si="4"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB6" s="17">
         <f t="shared" si="4"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC6" s="17">
         <f t="shared" si="4"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD6" s="17">
         <f t="shared" si="4"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE6" s="17">
         <f t="shared" si="4"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF6" s="17">
         <f t="shared" si="4"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG6" s="17">
         <f t="shared" si="4"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -39916,128 +44102,128 @@
         <v>1</v>
       </c>
       <c r="C7" s="17">
-        <f t="shared" ref="C7:AG7" si="5">B7-B7*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C7:AG7" si="5">B7-B7*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D7" s="17">
         <f t="shared" si="5"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E7" s="17">
         <f t="shared" si="5"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F7" s="17">
         <f t="shared" si="5"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="5"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="5"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="5"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J7" s="17">
         <f t="shared" si="5"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K7" s="17">
         <f t="shared" si="5"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L7" s="17">
         <f t="shared" si="5"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" si="5"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" si="5"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O7" s="17">
         <f t="shared" si="5"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P7" s="17">
         <f t="shared" si="5"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="5"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R7" s="17">
         <f t="shared" si="5"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S7" s="17">
         <f t="shared" si="5"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T7" s="17">
         <f t="shared" si="5"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U7" s="17">
         <f t="shared" si="5"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V7" s="17">
         <f t="shared" si="5"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W7" s="17">
         <f t="shared" si="5"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X7" s="17">
         <f t="shared" si="5"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y7" s="17">
         <f t="shared" si="5"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z7" s="17">
         <f t="shared" si="5"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA7" s="17">
         <f t="shared" si="5"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB7" s="17">
         <f t="shared" si="5"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC7" s="17">
         <f t="shared" si="5"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD7" s="17">
         <f t="shared" si="5"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE7" s="17">
         <f t="shared" si="5"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF7" s="17">
         <f t="shared" si="5"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG7" s="17">
         <f t="shared" si="5"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -40048,128 +44234,128 @@
         <v>1</v>
       </c>
       <c r="C8" s="17">
-        <f t="shared" ref="C8:AG8" si="6">B8-B8*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C8:AG8" si="6">B8-B8*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D8" s="17">
         <f t="shared" si="6"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E8" s="17">
         <f t="shared" si="6"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F8" s="17">
         <f t="shared" si="6"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="6"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="6"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="6"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J8" s="17">
         <f t="shared" si="6"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K8" s="17">
         <f t="shared" si="6"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L8" s="17">
         <f t="shared" si="6"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M8" s="17">
         <f t="shared" si="6"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="6"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O8" s="17">
         <f t="shared" si="6"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P8" s="17">
         <f t="shared" si="6"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="6"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R8" s="17">
         <f t="shared" si="6"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S8" s="17">
         <f t="shared" si="6"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T8" s="17">
         <f t="shared" si="6"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U8" s="17">
         <f t="shared" si="6"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V8" s="17">
         <f t="shared" si="6"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W8" s="17">
         <f t="shared" si="6"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X8" s="17">
         <f t="shared" si="6"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y8" s="17">
         <f t="shared" si="6"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z8" s="17">
         <f t="shared" si="6"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA8" s="17">
         <f t="shared" si="6"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB8" s="17">
         <f t="shared" si="6"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC8" s="17">
         <f t="shared" si="6"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD8" s="17">
         <f t="shared" si="6"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE8" s="17">
         <f t="shared" si="6"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF8" s="17">
         <f t="shared" si="6"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG8" s="17">
         <f t="shared" si="6"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -40180,128 +44366,128 @@
         <v>1</v>
       </c>
       <c r="C9" s="17">
-        <f t="shared" ref="C9:AG9" si="7">B9-B9*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C9:AG9" si="7">B9-B9*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D9" s="17">
         <f t="shared" si="7"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E9" s="17">
         <f t="shared" si="7"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F9" s="17">
         <f t="shared" si="7"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="7"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="7"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="7"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J9" s="17">
         <f t="shared" si="7"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K9" s="17">
         <f t="shared" si="7"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L9" s="17">
         <f t="shared" si="7"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M9" s="17">
         <f t="shared" si="7"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="7"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O9" s="17">
         <f t="shared" si="7"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P9" s="17">
         <f t="shared" si="7"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="7"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R9" s="17">
         <f t="shared" si="7"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S9" s="17">
         <f t="shared" si="7"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T9" s="17">
         <f t="shared" si="7"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U9" s="17">
         <f t="shared" si="7"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V9" s="17">
         <f t="shared" si="7"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W9" s="17">
         <f t="shared" si="7"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X9" s="17">
         <f t="shared" si="7"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y9" s="17">
         <f t="shared" si="7"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z9" s="17">
         <f t="shared" si="7"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA9" s="17">
         <f t="shared" si="7"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB9" s="17">
         <f t="shared" si="7"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC9" s="17">
         <f t="shared" si="7"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD9" s="17">
         <f t="shared" si="7"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE9" s="17">
         <f t="shared" si="7"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF9" s="17">
         <f t="shared" si="7"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG9" s="17">
         <f t="shared" si="7"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -40312,128 +44498,128 @@
         <v>1</v>
       </c>
       <c r="C10" s="17">
-        <f t="shared" ref="C10:AG10" si="8">B10-B10*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C10:AG10" si="8">B10-B10*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D10" s="17">
         <f t="shared" si="8"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E10" s="17">
         <f t="shared" si="8"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="8"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="8"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="8"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="8"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J10" s="17">
         <f t="shared" si="8"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K10" s="17">
         <f t="shared" si="8"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L10" s="17">
         <f t="shared" si="8"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M10" s="17">
         <f t="shared" si="8"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="8"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O10" s="17">
         <f t="shared" si="8"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P10" s="17">
         <f t="shared" si="8"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="8"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R10" s="17">
         <f t="shared" si="8"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S10" s="17">
         <f t="shared" si="8"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T10" s="17">
         <f t="shared" si="8"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U10" s="17">
         <f t="shared" si="8"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V10" s="17">
         <f t="shared" si="8"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W10" s="17">
         <f t="shared" si="8"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X10" s="17">
         <f t="shared" si="8"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y10" s="17">
         <f t="shared" si="8"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z10" s="17">
         <f t="shared" si="8"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA10" s="17">
         <f t="shared" si="8"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB10" s="17">
         <f t="shared" si="8"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC10" s="17">
         <f t="shared" si="8"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD10" s="17">
         <f t="shared" si="8"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE10" s="17">
         <f t="shared" si="8"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF10" s="17">
         <f t="shared" si="8"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG10" s="17">
         <f t="shared" si="8"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -40444,128 +44630,128 @@
         <v>1</v>
       </c>
       <c r="C11" s="17">
-        <f t="shared" ref="C11:AG11" si="9">B11-B11*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C11:AG11" si="9">B11-B11*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D11" s="17">
         <f t="shared" si="9"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E11" s="17">
         <f t="shared" si="9"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="9"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="9"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="9"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="9"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J11" s="17">
         <f t="shared" si="9"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K11" s="17">
         <f t="shared" si="9"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L11" s="17">
         <f t="shared" si="9"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M11" s="17">
         <f t="shared" si="9"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N11" s="17">
         <f t="shared" si="9"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O11" s="17">
         <f t="shared" si="9"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P11" s="17">
         <f t="shared" si="9"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="9"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R11" s="17">
         <f t="shared" si="9"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S11" s="17">
         <f t="shared" si="9"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T11" s="17">
         <f t="shared" si="9"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U11" s="17">
         <f t="shared" si="9"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V11" s="17">
         <f t="shared" si="9"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W11" s="17">
         <f t="shared" si="9"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X11" s="17">
         <f t="shared" si="9"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y11" s="17">
         <f t="shared" si="9"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z11" s="17">
         <f t="shared" si="9"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA11" s="17">
         <f t="shared" si="9"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB11" s="17">
         <f t="shared" si="9"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC11" s="17">
         <f t="shared" si="9"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD11" s="17">
         <f t="shared" si="9"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE11" s="17">
         <f t="shared" si="9"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF11" s="17">
         <f t="shared" si="9"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG11" s="17">
         <f t="shared" si="9"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -40576,128 +44762,128 @@
         <v>1</v>
       </c>
       <c r="C12" s="17">
-        <f t="shared" ref="C12:AG12" si="10">B12-B12*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C12:AG12" si="10">B12-B12*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D12" s="17">
         <f t="shared" si="10"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E12" s="17">
         <f t="shared" si="10"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="10"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="10"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" si="10"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="10"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J12" s="17">
         <f t="shared" si="10"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K12" s="17">
         <f t="shared" si="10"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L12" s="17">
         <f t="shared" si="10"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M12" s="17">
         <f t="shared" si="10"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N12" s="17">
         <f t="shared" si="10"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O12" s="17">
         <f t="shared" si="10"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P12" s="17">
         <f t="shared" si="10"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q12" s="17">
         <f t="shared" si="10"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R12" s="17">
         <f t="shared" si="10"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S12" s="17">
         <f t="shared" si="10"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T12" s="17">
         <f t="shared" si="10"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U12" s="17">
         <f t="shared" si="10"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V12" s="17">
         <f t="shared" si="10"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W12" s="17">
         <f t="shared" si="10"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X12" s="17">
         <f t="shared" si="10"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y12" s="17">
         <f t="shared" si="10"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z12" s="17">
         <f t="shared" si="10"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA12" s="17">
         <f t="shared" si="10"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB12" s="17">
         <f t="shared" si="10"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC12" s="17">
         <f t="shared" si="10"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD12" s="17">
         <f t="shared" si="10"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE12" s="17">
         <f t="shared" si="10"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF12" s="17">
         <f t="shared" si="10"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG12" s="17">
         <f t="shared" si="10"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -40708,128 +44894,128 @@
         <v>1</v>
       </c>
       <c r="C13" s="17">
-        <f t="shared" ref="C13:AG13" si="11">B13-B13*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C13:AG13" si="11">B13-B13*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D13" s="17">
         <f t="shared" si="11"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E13" s="17">
         <f t="shared" si="11"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F13" s="17">
         <f t="shared" si="11"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="11"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H13" s="17">
         <f t="shared" si="11"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="11"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J13" s="17">
         <f t="shared" si="11"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K13" s="17">
         <f t="shared" si="11"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L13" s="17">
         <f t="shared" si="11"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M13" s="17">
         <f t="shared" si="11"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N13" s="17">
         <f t="shared" si="11"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O13" s="17">
         <f t="shared" si="11"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P13" s="17">
         <f t="shared" si="11"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="11"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R13" s="17">
         <f t="shared" si="11"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S13" s="17">
         <f t="shared" si="11"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T13" s="17">
         <f t="shared" si="11"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U13" s="17">
         <f t="shared" si="11"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V13" s="17">
         <f t="shared" si="11"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W13" s="17">
         <f t="shared" si="11"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X13" s="17">
         <f t="shared" si="11"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y13" s="17">
         <f t="shared" si="11"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z13" s="17">
         <f t="shared" si="11"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA13" s="17">
         <f t="shared" si="11"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB13" s="17">
         <f t="shared" si="11"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC13" s="17">
         <f t="shared" si="11"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD13" s="17">
         <f t="shared" si="11"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE13" s="17">
         <f t="shared" si="11"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF13" s="17">
         <f t="shared" si="11"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG13" s="17">
         <f t="shared" si="11"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -40840,128 +45026,128 @@
         <v>1</v>
       </c>
       <c r="C14" s="17">
-        <f t="shared" ref="C14:AG14" si="12">B14-B14*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C14:AG14" si="12">B14-B14*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D14" s="17">
         <f t="shared" si="12"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E14" s="17">
         <f t="shared" si="12"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="12"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="12"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H14" s="17">
         <f t="shared" si="12"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="12"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J14" s="17">
         <f t="shared" si="12"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K14" s="17">
         <f t="shared" si="12"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L14" s="17">
         <f t="shared" si="12"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M14" s="17">
         <f t="shared" si="12"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N14" s="17">
         <f t="shared" si="12"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O14" s="17">
         <f t="shared" si="12"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P14" s="17">
         <f t="shared" si="12"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="12"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R14" s="17">
         <f t="shared" si="12"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S14" s="17">
         <f t="shared" si="12"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T14" s="17">
         <f t="shared" si="12"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U14" s="17">
         <f t="shared" si="12"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V14" s="17">
         <f t="shared" si="12"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W14" s="17">
         <f t="shared" si="12"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X14" s="17">
         <f t="shared" si="12"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y14" s="17">
         <f t="shared" si="12"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z14" s="17">
         <f t="shared" si="12"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="12"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB14" s="17">
         <f t="shared" si="12"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC14" s="17">
         <f t="shared" si="12"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD14" s="17">
         <f t="shared" si="12"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE14" s="17">
         <f t="shared" si="12"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF14" s="17">
         <f t="shared" si="12"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG14" s="17">
         <f t="shared" si="12"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -40972,128 +45158,128 @@
         <v>1</v>
       </c>
       <c r="C15" s="17">
-        <f t="shared" ref="C15:AG15" si="13">B15-B15*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C15:AG15" si="13">B15-B15*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D15" s="17">
         <f t="shared" si="13"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E15" s="17">
         <f t="shared" si="13"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" si="13"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="13"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" si="13"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I15" s="17">
         <f t="shared" si="13"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J15" s="17">
         <f t="shared" si="13"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K15" s="17">
         <f t="shared" si="13"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L15" s="17">
         <f t="shared" si="13"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M15" s="17">
         <f t="shared" si="13"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N15" s="17">
         <f t="shared" si="13"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O15" s="17">
         <f t="shared" si="13"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P15" s="17">
         <f t="shared" si="13"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="13"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R15" s="17">
         <f t="shared" si="13"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S15" s="17">
         <f t="shared" si="13"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T15" s="17">
         <f t="shared" si="13"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U15" s="17">
         <f t="shared" si="13"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V15" s="17">
         <f t="shared" si="13"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W15" s="17">
         <f t="shared" si="13"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X15" s="17">
         <f t="shared" si="13"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y15" s="17">
         <f t="shared" si="13"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z15" s="17">
         <f t="shared" si="13"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB15" s="17">
         <f t="shared" si="13"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC15" s="17">
         <f t="shared" si="13"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD15" s="17">
         <f t="shared" si="13"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE15" s="17">
         <f t="shared" si="13"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF15" s="17">
         <f t="shared" si="13"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG15" s="17">
         <f t="shared" si="13"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -41104,128 +45290,128 @@
         <v>1</v>
       </c>
       <c r="C16" s="17">
-        <f t="shared" ref="C16:AG16" si="14">B16-B16*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C16:AG16" si="14">B16-B16*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D16" s="17">
         <f t="shared" si="14"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E16" s="17">
         <f t="shared" si="14"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="14"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G16" s="17">
         <f t="shared" si="14"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H16" s="17">
         <f t="shared" si="14"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="14"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J16" s="17">
         <f t="shared" si="14"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K16" s="17">
         <f t="shared" si="14"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L16" s="17">
         <f t="shared" si="14"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M16" s="17">
         <f t="shared" si="14"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N16" s="17">
         <f t="shared" si="14"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O16" s="17">
         <f t="shared" si="14"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P16" s="17">
         <f t="shared" si="14"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="14"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R16" s="17">
         <f t="shared" si="14"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S16" s="17">
         <f t="shared" si="14"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T16" s="17">
         <f t="shared" si="14"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U16" s="17">
         <f t="shared" si="14"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V16" s="17">
         <f t="shared" si="14"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W16" s="17">
         <f t="shared" si="14"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X16" s="17">
         <f t="shared" si="14"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y16" s="17">
         <f t="shared" si="14"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z16" s="17">
         <f t="shared" si="14"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="14"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB16" s="17">
         <f t="shared" si="14"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC16" s="17">
         <f t="shared" si="14"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD16" s="17">
         <f t="shared" si="14"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE16" s="17">
         <f t="shared" si="14"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF16" s="17">
         <f t="shared" si="14"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG16" s="17">
         <f t="shared" si="14"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -41236,128 +45422,128 @@
         <v>1</v>
       </c>
       <c r="C17" s="17">
-        <f t="shared" ref="C17:AG17" si="15">B17-B17*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C17:AG17" si="15">B17-B17*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D17" s="17">
         <f t="shared" si="15"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E17" s="17">
         <f t="shared" si="15"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F17" s="17">
         <f t="shared" si="15"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G17" s="17">
         <f t="shared" si="15"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" si="15"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="15"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J17" s="17">
         <f t="shared" si="15"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K17" s="17">
         <f t="shared" si="15"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L17" s="17">
         <f t="shared" si="15"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M17" s="17">
         <f t="shared" si="15"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N17" s="17">
         <f t="shared" si="15"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O17" s="17">
         <f t="shared" si="15"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P17" s="17">
         <f t="shared" si="15"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q17" s="17">
         <f t="shared" si="15"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R17" s="17">
         <f t="shared" si="15"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S17" s="17">
         <f t="shared" si="15"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T17" s="17">
         <f t="shared" si="15"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U17" s="17">
         <f t="shared" si="15"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V17" s="17">
         <f t="shared" si="15"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W17" s="17">
         <f t="shared" si="15"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X17" s="17">
         <f t="shared" si="15"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y17" s="17">
         <f t="shared" si="15"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z17" s="17">
         <f t="shared" si="15"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="15"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB17" s="17">
         <f t="shared" si="15"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC17" s="17">
         <f t="shared" si="15"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD17" s="17">
         <f t="shared" si="15"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE17" s="17">
         <f t="shared" si="15"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF17" s="17">
         <f t="shared" si="15"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG17" s="17">
         <f t="shared" si="15"/>
-        <v>0.53457463299478836</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
@@ -41368,1960 +45554,128 @@
         <v>1</v>
       </c>
       <c r="C18" s="17">
-        <f t="shared" ref="C18:AG18" si="16">B18-B18*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C18:AG18" si="16">B18-B18*0.01</f>
+        <v>0.99</v>
       </c>
       <c r="D18" s="17">
         <f t="shared" si="16"/>
-        <v>0.96040000000000003</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E18" s="17">
         <f t="shared" si="16"/>
-        <v>0.94119200000000003</v>
+        <v>0.97029900000000002</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="16"/>
-        <v>0.92236815999999999</v>
+        <v>0.96059601000000006</v>
       </c>
       <c r="G18" s="17">
         <f t="shared" si="16"/>
-        <v>0.90392079680000004</v>
+        <v>0.95099004990000002</v>
       </c>
       <c r="H18" s="17">
         <f t="shared" si="16"/>
-        <v>0.88584238086400002</v>
+        <v>0.941480149401</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="16"/>
-        <v>0.86812553324672004</v>
+        <v>0.93206534790699003</v>
       </c>
       <c r="J18" s="17">
         <f t="shared" si="16"/>
-        <v>0.8507630225817856</v>
+        <v>0.92274469442792018</v>
       </c>
       <c r="K18" s="17">
         <f t="shared" si="16"/>
-        <v>0.83374776213014989</v>
+        <v>0.91351724748364094</v>
       </c>
       <c r="L18" s="17">
         <f t="shared" si="16"/>
-        <v>0.81707280688754691</v>
+        <v>0.90438207500880452</v>
       </c>
       <c r="M18" s="17">
         <f t="shared" si="16"/>
-        <v>0.80073135074979596</v>
+        <v>0.89533825425871649</v>
       </c>
       <c r="N18" s="17">
         <f t="shared" si="16"/>
-        <v>0.78471672373480006</v>
+        <v>0.88638487171612934</v>
       </c>
       <c r="O18" s="17">
         <f t="shared" si="16"/>
-        <v>0.76902238926010402</v>
+        <v>0.87752102299896806</v>
       </c>
       <c r="P18" s="17">
         <f t="shared" si="16"/>
-        <v>0.75364194147490193</v>
+        <v>0.86874581276897833</v>
       </c>
       <c r="Q18" s="17">
         <f t="shared" si="16"/>
-        <v>0.73856910264540387</v>
+        <v>0.86005835464128855</v>
       </c>
       <c r="R18" s="17">
         <f t="shared" si="16"/>
-        <v>0.72379772059249581</v>
+        <v>0.85145777109487564</v>
       </c>
       <c r="S18" s="17">
         <f t="shared" si="16"/>
-        <v>0.70932176618064591</v>
+        <v>0.84294319338392687</v>
       </c>
       <c r="T18" s="17">
         <f t="shared" si="16"/>
-        <v>0.69513533085703294</v>
+        <v>0.8345137614500876</v>
       </c>
       <c r="U18" s="17">
         <f t="shared" si="16"/>
-        <v>0.68123262423989228</v>
+        <v>0.82616862383558676</v>
       </c>
       <c r="V18" s="17">
         <f t="shared" si="16"/>
-        <v>0.66760797175509445</v>
+        <v>0.81790693759723088</v>
       </c>
       <c r="W18" s="17">
         <f t="shared" si="16"/>
-        <v>0.65425581231999252</v>
+        <v>0.80972786822125853</v>
       </c>
       <c r="X18" s="17">
         <f t="shared" si="16"/>
-        <v>0.64117069607359267</v>
+        <v>0.80163058953904598</v>
       </c>
       <c r="Y18" s="17">
         <f t="shared" si="16"/>
-        <v>0.62834728215212077</v>
+        <v>0.79361428364365549</v>
       </c>
       <c r="Z18" s="17">
         <f t="shared" si="16"/>
-        <v>0.61578033650907837</v>
+        <v>0.78567814080721898</v>
       </c>
       <c r="AA18" s="17">
         <f t="shared" si="16"/>
-        <v>0.60346472977889676</v>
+        <v>0.77782135939914676</v>
       </c>
       <c r="AB18" s="17">
         <f t="shared" si="16"/>
-        <v>0.59139543518331883</v>
+        <v>0.77004314580515532</v>
       </c>
       <c r="AC18" s="17">
         <f t="shared" si="16"/>
-        <v>0.57956752647965248</v>
+        <v>0.76234271434710377</v>
       </c>
       <c r="AD18" s="17">
         <f t="shared" si="16"/>
-        <v>0.56797617595005945</v>
+        <v>0.75471928720363268</v>
       </c>
       <c r="AE18" s="17">
         <f t="shared" si="16"/>
-        <v>0.55661665243105829</v>
+        <v>0.74717209433159637</v>
       </c>
       <c r="AF18" s="17">
         <f t="shared" si="16"/>
-        <v>0.54548431938243713</v>
+        <v>0.73970037338828043</v>
       </c>
       <c r="AG18" s="17">
         <f t="shared" si="16"/>
-        <v>0.53457463299478836</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B93DD5-A57F-41E3-A40A-188EC63D5E77}">
-  <dimension ref="A1:AG18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="33" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="16">
-        <v>2019</v>
-      </c>
-      <c r="C1" s="16">
-        <v>2020</v>
-      </c>
-      <c r="D1" s="16">
-        <v>2021</v>
-      </c>
-      <c r="E1" s="16">
-        <v>2022</v>
-      </c>
-      <c r="F1" s="16">
-        <v>2023</v>
-      </c>
-      <c r="G1" s="16">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="16">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="16">
-        <v>2026</v>
-      </c>
-      <c r="J1" s="16">
-        <v>2027</v>
-      </c>
-      <c r="K1" s="16">
-        <v>2028</v>
-      </c>
-      <c r="L1" s="16">
-        <v>2029</v>
-      </c>
-      <c r="M1" s="16">
-        <v>2030</v>
-      </c>
-      <c r="N1" s="16">
-        <v>2031</v>
-      </c>
-      <c r="O1" s="16">
-        <v>2032</v>
-      </c>
-      <c r="P1" s="16">
-        <v>2033</v>
-      </c>
-      <c r="Q1" s="16">
-        <v>2034</v>
-      </c>
-      <c r="R1" s="16">
-        <v>2035</v>
-      </c>
-      <c r="S1" s="16">
-        <v>2036</v>
-      </c>
-      <c r="T1" s="16">
-        <v>2037</v>
-      </c>
-      <c r="U1" s="16">
-        <v>2038</v>
-      </c>
-      <c r="V1" s="16">
-        <v>2039</v>
-      </c>
-      <c r="W1" s="16">
-        <v>2040</v>
-      </c>
-      <c r="X1" s="16">
-        <v>2041</v>
-      </c>
-      <c r="Y1" s="16">
-        <v>2042</v>
-      </c>
-      <c r="Z1" s="16">
-        <v>2043</v>
-      </c>
-      <c r="AA1" s="16">
-        <v>2044</v>
-      </c>
-      <c r="AB1" s="16">
-        <v>2045</v>
-      </c>
-      <c r="AC1" s="16">
-        <v>2046</v>
-      </c>
-      <c r="AD1" s="16">
-        <v>2047</v>
-      </c>
-      <c r="AE1" s="16">
-        <v>2048</v>
-      </c>
-      <c r="AF1" s="16">
-        <v>2049</v>
-      </c>
-      <c r="AG1" s="16">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0.97</v>
-      </c>
-      <c r="D2">
-        <v>0.9506</v>
-      </c>
-      <c r="E2">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F2">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G2">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H2">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I2">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J2">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K2">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L2">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M2">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N2">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O2">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P2">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q2">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R2">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S2">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T2">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U2">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V2">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W2">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X2">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y2">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z2">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA2">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB2">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC2">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD2">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE2">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF2">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG2">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1.02</v>
-      </c>
-      <c r="D3">
-        <v>0.99960000000000004</v>
-      </c>
-      <c r="E3">
-        <v>0.97960800000000003</v>
-      </c>
-      <c r="F3">
-        <v>0.96001584000000006</v>
-      </c>
-      <c r="G3">
-        <v>0.94081552320000006</v>
-      </c>
-      <c r="H3">
-        <v>0.92199921273600005</v>
-      </c>
-      <c r="I3">
-        <v>0.90355922848128001</v>
-      </c>
-      <c r="J3">
-        <v>0.88548804391165437</v>
-      </c>
-      <c r="K3">
-        <v>0.8677782830334213</v>
-      </c>
-      <c r="L3">
-        <v>0.85042271737275288</v>
-      </c>
-      <c r="M3">
-        <v>0.83341426302529786</v>
-      </c>
-      <c r="N3">
-        <v>0.81674597776479185</v>
-      </c>
-      <c r="O3">
-        <v>0.80041105820949598</v>
-      </c>
-      <c r="P3">
-        <v>0.78440283704530611</v>
-      </c>
-      <c r="Q3">
-        <v>0.76871478030439999</v>
-      </c>
-      <c r="R3">
-        <v>0.75334048469831194</v>
-      </c>
-      <c r="S3">
-        <v>0.73827367500434571</v>
-      </c>
-      <c r="T3">
-        <v>0.72350820150425876</v>
-      </c>
-      <c r="U3">
-        <v>0.7090380374741736</v>
-      </c>
-      <c r="V3">
-        <v>0.69485727672469011</v>
-      </c>
-      <c r="W3">
-        <v>0.68096013119019627</v>
-      </c>
-      <c r="X3">
-        <v>0.66734092856639238</v>
-      </c>
-      <c r="Y3">
-        <v>0.65399410999506458</v>
-      </c>
-      <c r="Z3">
-        <v>0.64091422779516327</v>
-      </c>
-      <c r="AA3">
-        <v>0.62809594323925999</v>
-      </c>
-      <c r="AB3">
-        <v>0.6155340243744748</v>
-      </c>
-      <c r="AC3">
-        <v>0.60322334388698529</v>
-      </c>
-      <c r="AD3">
-        <v>0.59115887700924563</v>
-      </c>
-      <c r="AE3">
-        <v>0.57933569946906072</v>
-      </c>
-      <c r="AF3">
-        <v>0.56774898547967956</v>
-      </c>
-      <c r="AG3">
-        <v>0.55639400577008602</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>0.97</v>
-      </c>
-      <c r="D4">
-        <v>0.94574999999999998</v>
-      </c>
-      <c r="E4">
-        <v>0.92210625000000002</v>
-      </c>
-      <c r="F4">
-        <v>0.89905359375000005</v>
-      </c>
-      <c r="G4">
-        <v>0.87657725390625008</v>
-      </c>
-      <c r="H4">
-        <v>0.85466282255859383</v>
-      </c>
-      <c r="I4">
-        <v>0.83329625199462898</v>
-      </c>
-      <c r="J4">
-        <v>0.81246384569476326</v>
-      </c>
-      <c r="K4">
-        <v>0.79215224955239416</v>
-      </c>
-      <c r="L4">
-        <v>0.77234844331358432</v>
-      </c>
-      <c r="M4">
-        <v>0.75303973223074472</v>
-      </c>
-      <c r="N4">
-        <v>0.7342137389249761</v>
-      </c>
-      <c r="O4">
-        <v>0.7158583954518517</v>
-      </c>
-      <c r="P4">
-        <v>0.69796193556555541</v>
-      </c>
-      <c r="Q4">
-        <v>0.68051288717641656</v>
-      </c>
-      <c r="R4">
-        <v>0.6635000649970062</v>
-      </c>
-      <c r="S4">
-        <v>0.64691256337208103</v>
-      </c>
-      <c r="T4">
-        <v>0.63073974928777898</v>
-      </c>
-      <c r="U4">
-        <v>0.61497125555558452</v>
-      </c>
-      <c r="V4">
-        <v>0.59959697416669488</v>
-      </c>
-      <c r="W4">
-        <v>0.58460704981252753</v>
-      </c>
-      <c r="X4">
-        <v>0.56999187356721437</v>
-      </c>
-      <c r="Y4">
-        <v>0.555742076728034</v>
-      </c>
-      <c r="Z4">
-        <v>0.54184852480983314</v>
-      </c>
-      <c r="AA4">
-        <v>0.5283023116895873</v>
-      </c>
-      <c r="AB4">
-        <v>0.5150947538973476</v>
-      </c>
-      <c r="AC4">
-        <v>0.50221738504991387</v>
-      </c>
-      <c r="AD4">
-        <v>0.489661950423666</v>
-      </c>
-      <c r="AE4">
-        <v>0.47742040166307437</v>
-      </c>
-      <c r="AF4">
-        <v>0.46548489162149753</v>
-      </c>
-      <c r="AG4">
-        <v>0.4538477693309601</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0.97</v>
-      </c>
-      <c r="D5">
-        <v>0.96514999999999995</v>
-      </c>
-      <c r="E5">
-        <v>0.96032424999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.95552262874999994</v>
-      </c>
-      <c r="G5">
-        <v>0.95074501560624991</v>
-      </c>
-      <c r="H5">
-        <v>0.94599129052821862</v>
-      </c>
-      <c r="I5">
-        <v>0.94126133407557755</v>
-      </c>
-      <c r="J5">
-        <v>0.93655502740519969</v>
-      </c>
-      <c r="K5">
-        <v>0.93187225226817372</v>
-      </c>
-      <c r="L5">
-        <v>0.9272128910068328</v>
-      </c>
-      <c r="M5">
-        <v>0.92257682655179862</v>
-      </c>
-      <c r="N5">
-        <v>0.91796394241903967</v>
-      </c>
-      <c r="O5">
-        <v>0.91337412270694451</v>
-      </c>
-      <c r="P5">
-        <v>0.90880725209340985</v>
-      </c>
-      <c r="Q5">
-        <v>0.90426321583294278</v>
-      </c>
-      <c r="R5">
-        <v>0.89974189975377805</v>
-      </c>
-      <c r="S5">
-        <v>0.8952431902550092</v>
-      </c>
-      <c r="T5">
-        <v>0.89076697430373419</v>
-      </c>
-      <c r="U5">
-        <v>0.88631313943221557</v>
-      </c>
-      <c r="V5">
-        <v>0.88188157373505449</v>
-      </c>
-      <c r="W5">
-        <v>0.87747216586637922</v>
-      </c>
-      <c r="X5">
-        <v>0.87308480503704733</v>
-      </c>
-      <c r="Y5">
-        <v>0.86871938101186208</v>
-      </c>
-      <c r="Z5">
-        <v>0.86437578410680271</v>
-      </c>
-      <c r="AA5">
-        <v>0.86005390518626867</v>
-      </c>
-      <c r="AB5">
-        <v>0.85575363566033735</v>
-      </c>
-      <c r="AC5">
-        <v>0.85147486748203571</v>
-      </c>
-      <c r="AD5">
-        <v>0.84721749314462558</v>
-      </c>
-      <c r="AE5">
-        <v>0.84298140567890245</v>
-      </c>
-      <c r="AF5">
-        <v>0.8387664986505079</v>
-      </c>
-      <c r="AG5">
-        <v>0.83457266615725534</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0.97</v>
-      </c>
-      <c r="D6">
-        <v>0.96514999999999995</v>
-      </c>
-      <c r="E6">
-        <v>0.96032424999999999</v>
-      </c>
-      <c r="F6">
-        <v>0.95552262874999994</v>
-      </c>
-      <c r="G6">
-        <v>0.95074501560624991</v>
-      </c>
-      <c r="H6">
-        <v>0.94599129052821862</v>
-      </c>
-      <c r="I6">
-        <v>0.94126133407557755</v>
-      </c>
-      <c r="J6">
-        <v>0.93655502740519969</v>
-      </c>
-      <c r="K6">
-        <v>0.93187225226817372</v>
-      </c>
-      <c r="L6">
-        <v>0.9272128910068328</v>
-      </c>
-      <c r="M6">
-        <v>0.92257682655179862</v>
-      </c>
-      <c r="N6">
-        <v>0.91796394241903967</v>
-      </c>
-      <c r="O6">
-        <v>0.91337412270694451</v>
-      </c>
-      <c r="P6">
-        <v>0.90880725209340985</v>
-      </c>
-      <c r="Q6">
-        <v>0.90426321583294278</v>
-      </c>
-      <c r="R6">
-        <v>0.89974189975377805</v>
-      </c>
-      <c r="S6">
-        <v>0.8952431902550092</v>
-      </c>
-      <c r="T6">
-        <v>0.89076697430373419</v>
-      </c>
-      <c r="U6">
-        <v>0.88631313943221557</v>
-      </c>
-      <c r="V6">
-        <v>0.88188157373505449</v>
-      </c>
-      <c r="W6">
-        <v>0.87747216586637922</v>
-      </c>
-      <c r="X6">
-        <v>0.87308480503704733</v>
-      </c>
-      <c r="Y6">
-        <v>0.86871938101186208</v>
-      </c>
-      <c r="Z6">
-        <v>0.86437578410680271</v>
-      </c>
-      <c r="AA6">
-        <v>0.86005390518626867</v>
-      </c>
-      <c r="AB6">
-        <v>0.85575363566033735</v>
-      </c>
-      <c r="AC6">
-        <v>0.85147486748203571</v>
-      </c>
-      <c r="AD6">
-        <v>0.84721749314462558</v>
-      </c>
-      <c r="AE6">
-        <v>0.84298140567890245</v>
-      </c>
-      <c r="AF6">
-        <v>0.8387664986505079</v>
-      </c>
-      <c r="AG6">
-        <v>0.83457266615725534</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0.97</v>
-      </c>
-      <c r="D7">
-        <v>0.96514999999999995</v>
-      </c>
-      <c r="E7">
-        <v>0.96032424999999999</v>
-      </c>
-      <c r="F7">
-        <v>0.95552262874999994</v>
-      </c>
-      <c r="G7">
-        <v>0.95074501560624991</v>
-      </c>
-      <c r="H7">
-        <v>0.94599129052821862</v>
-      </c>
-      <c r="I7">
-        <v>0.94126133407557755</v>
-      </c>
-      <c r="J7">
-        <v>0.93655502740519969</v>
-      </c>
-      <c r="K7">
-        <v>0.93187225226817372</v>
-      </c>
-      <c r="L7">
-        <v>0.9272128910068328</v>
-      </c>
-      <c r="M7">
-        <v>0.92257682655179862</v>
-      </c>
-      <c r="N7">
-        <v>0.91796394241903967</v>
-      </c>
-      <c r="O7">
-        <v>0.91337412270694451</v>
-      </c>
-      <c r="P7">
-        <v>0.90880725209340985</v>
-      </c>
-      <c r="Q7">
-        <v>0.90426321583294278</v>
-      </c>
-      <c r="R7">
-        <v>0.89974189975377805</v>
-      </c>
-      <c r="S7">
-        <v>0.8952431902550092</v>
-      </c>
-      <c r="T7">
-        <v>0.89076697430373419</v>
-      </c>
-      <c r="U7">
-        <v>0.88631313943221557</v>
-      </c>
-      <c r="V7">
-        <v>0.88188157373505449</v>
-      </c>
-      <c r="W7">
-        <v>0.87747216586637922</v>
-      </c>
-      <c r="X7">
-        <v>0.87308480503704733</v>
-      </c>
-      <c r="Y7">
-        <v>0.86871938101186208</v>
-      </c>
-      <c r="Z7">
-        <v>0.86437578410680271</v>
-      </c>
-      <c r="AA7">
-        <v>0.86005390518626867</v>
-      </c>
-      <c r="AB7">
-        <v>0.85575363566033735</v>
-      </c>
-      <c r="AC7">
-        <v>0.85147486748203571</v>
-      </c>
-      <c r="AD7">
-        <v>0.84721749314462558</v>
-      </c>
-      <c r="AE7">
-        <v>0.84298140567890245</v>
-      </c>
-      <c r="AF7">
-        <v>0.8387664986505079</v>
-      </c>
-      <c r="AG7">
-        <v>0.83457266615725534</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0.97</v>
-      </c>
-      <c r="D8">
-        <v>0.9506</v>
-      </c>
-      <c r="E8">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F8">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G8">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H8">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I8">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J8">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K8">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L8">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M8">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N8">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O8">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P8">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q8">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R8">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S8">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T8">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U8">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V8">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W8">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X8">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y8">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z8">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA8">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB8">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC8">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD8">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE8">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF8">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG8">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>0.97</v>
-      </c>
-      <c r="D9">
-        <v>0.96029999999999993</v>
-      </c>
-      <c r="E9">
-        <v>0.9506969999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.9411900299999999</v>
-      </c>
-      <c r="G9">
-        <v>0.93177812969999985</v>
-      </c>
-      <c r="H9">
-        <v>0.92246034840299984</v>
-      </c>
-      <c r="I9">
-        <v>0.91323574491896986</v>
-      </c>
-      <c r="J9">
-        <v>0.90410338746978014</v>
-      </c>
-      <c r="K9">
-        <v>0.89506235359508235</v>
-      </c>
-      <c r="L9">
-        <v>0.88611173005913157</v>
-      </c>
-      <c r="M9">
-        <v>0.87725061275854022</v>
-      </c>
-      <c r="N9">
-        <v>0.86847810663095482</v>
-      </c>
-      <c r="O9">
-        <v>0.85979332556464527</v>
-      </c>
-      <c r="P9">
-        <v>0.85119539230899877</v>
-      </c>
-      <c r="Q9">
-        <v>0.84268343838590876</v>
-      </c>
-      <c r="R9">
-        <v>0.83425660400204971</v>
-      </c>
-      <c r="S9">
-        <v>0.82591403796202922</v>
-      </c>
-      <c r="T9">
-        <v>0.81765489758240895</v>
-      </c>
-      <c r="U9">
-        <v>0.80947834860658485</v>
-      </c>
-      <c r="V9">
-        <v>0.801383565120519</v>
-      </c>
-      <c r="W9">
-        <v>0.79336972946931383</v>
-      </c>
-      <c r="X9">
-        <v>0.78543603217462066</v>
-      </c>
-      <c r="Y9">
-        <v>0.77758167185287441</v>
-      </c>
-      <c r="Z9">
-        <v>0.76980585513434563</v>
-      </c>
-      <c r="AA9">
-        <v>0.76210779658300221</v>
-      </c>
-      <c r="AB9">
-        <v>0.7544867186171722</v>
-      </c>
-      <c r="AC9">
-        <v>0.74694185143100045</v>
-      </c>
-      <c r="AD9">
-        <v>0.7394724329166904</v>
-      </c>
-      <c r="AE9">
-        <v>0.73207770858752352</v>
-      </c>
-      <c r="AF9">
-        <v>0.72475693150164833</v>
-      </c>
-      <c r="AG9">
-        <v>0.71750936218663186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0.97</v>
-      </c>
-      <c r="D10">
-        <v>0.94089999999999996</v>
-      </c>
-      <c r="E10">
-        <v>0.91737749999999996</v>
-      </c>
-      <c r="F10">
-        <v>0.89444306249999994</v>
-      </c>
-      <c r="G10">
-        <v>0.87208198593749997</v>
-      </c>
-      <c r="H10">
-        <v>0.85027993628906251</v>
-      </c>
-      <c r="I10">
-        <v>0.8290229378818359</v>
-      </c>
-      <c r="J10">
-        <v>0.80829736443478994</v>
-      </c>
-      <c r="K10">
-        <v>0.78808993032392016</v>
-      </c>
-      <c r="L10">
-        <v>0.7683876820658222</v>
-      </c>
-      <c r="M10">
-        <v>0.74917799001417662</v>
-      </c>
-      <c r="N10">
-        <v>0.72670265031375136</v>
-      </c>
-      <c r="O10">
-        <v>0.7049015708043388</v>
-      </c>
-      <c r="P10">
-        <v>0.68375452368020861</v>
-      </c>
-      <c r="Q10">
-        <v>0.66324188796980232</v>
-      </c>
-      <c r="R10">
-        <v>0.64334463133070829</v>
-      </c>
-      <c r="S10">
-        <v>0.62404429239078707</v>
-      </c>
-      <c r="T10">
-        <v>0.60532296361906346</v>
-      </c>
-      <c r="U10">
-        <v>0.58716327471049157</v>
-      </c>
-      <c r="V10">
-        <v>0.56954837646917678</v>
-      </c>
-      <c r="W10">
-        <v>0.55246192517510151</v>
-      </c>
-      <c r="X10">
-        <v>0.53588806741984851</v>
-      </c>
-      <c r="Y10">
-        <v>0.519811425397253</v>
-      </c>
-      <c r="Z10">
-        <v>0.50421708263533538</v>
-      </c>
-      <c r="AA10">
-        <v>0.48909057015627533</v>
-      </c>
-      <c r="AB10">
-        <v>0.47441785305158707</v>
-      </c>
-      <c r="AC10">
-        <v>0.46018531746003943</v>
-      </c>
-      <c r="AD10">
-        <v>0.44637975793623824</v>
-      </c>
-      <c r="AE10">
-        <v>0.43298836519815109</v>
-      </c>
-      <c r="AF10">
-        <v>0.41999871424220658</v>
-      </c>
-      <c r="AG10">
-        <v>0.40739875281494037</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>0.97</v>
-      </c>
-      <c r="D11">
-        <v>0.96514999999999995</v>
-      </c>
-      <c r="E11">
-        <v>0.96032424999999999</v>
-      </c>
-      <c r="F11">
-        <v>0.95552262874999994</v>
-      </c>
-      <c r="G11">
-        <v>0.95074501560624991</v>
-      </c>
-      <c r="H11">
-        <v>0.94599129052821862</v>
-      </c>
-      <c r="I11">
-        <v>0.94126133407557755</v>
-      </c>
-      <c r="J11">
-        <v>0.93655502740519969</v>
-      </c>
-      <c r="K11">
-        <v>0.93187225226817372</v>
-      </c>
-      <c r="L11">
-        <v>0.9272128910068328</v>
-      </c>
-      <c r="M11">
-        <v>0.92257682655179862</v>
-      </c>
-      <c r="N11">
-        <v>0.91796394241903967</v>
-      </c>
-      <c r="O11">
-        <v>0.91337412270694451</v>
-      </c>
-      <c r="P11">
-        <v>0.90880725209340985</v>
-      </c>
-      <c r="Q11">
-        <v>0.90426321583294278</v>
-      </c>
-      <c r="R11">
-        <v>0.89974189975377805</v>
-      </c>
-      <c r="S11">
-        <v>0.8952431902550092</v>
-      </c>
-      <c r="T11">
-        <v>0.89076697430373419</v>
-      </c>
-      <c r="U11">
-        <v>0.88631313943221557</v>
-      </c>
-      <c r="V11">
-        <v>0.88188157373505449</v>
-      </c>
-      <c r="W11">
-        <v>0.87747216586637922</v>
-      </c>
-      <c r="X11">
-        <v>0.87308480503704733</v>
-      </c>
-      <c r="Y11">
-        <v>0.86871938101186208</v>
-      </c>
-      <c r="Z11">
-        <v>0.86437578410680271</v>
-      </c>
-      <c r="AA11">
-        <v>0.86005390518626867</v>
-      </c>
-      <c r="AB11">
-        <v>0.85575363566033735</v>
-      </c>
-      <c r="AC11">
-        <v>0.85147486748203571</v>
-      </c>
-      <c r="AD11">
-        <v>0.84721749314462558</v>
-      </c>
-      <c r="AE11">
-        <v>0.84298140567890245</v>
-      </c>
-      <c r="AF11">
-        <v>0.8387664986505079</v>
-      </c>
-      <c r="AG11">
-        <v>0.83457266615725534</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>0.97</v>
-      </c>
-      <c r="D12">
-        <v>0.9506</v>
-      </c>
-      <c r="E12">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F12">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G12">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H12">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I12">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J12">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K12">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L12">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M12">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N12">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O12">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P12">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q12">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R12">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S12">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T12">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U12">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V12">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W12">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X12">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y12">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z12">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA12">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB12">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC12">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD12">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE12">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF12">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG12">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>0.97</v>
-      </c>
-      <c r="D13">
-        <v>0.9506</v>
-      </c>
-      <c r="E13">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F13">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G13">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H13">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I13">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J13">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K13">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L13">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M13">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N13">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O13">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P13">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q13">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R13">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S13">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T13">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U13">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V13">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W13">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X13">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y13">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z13">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA13">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB13">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC13">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD13">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE13">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF13">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG13">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>0.97</v>
-      </c>
-      <c r="D14">
-        <v>0.96029999999999993</v>
-      </c>
-      <c r="E14">
-        <v>0.9506969999999999</v>
-      </c>
-      <c r="F14">
-        <v>0.9411900299999999</v>
-      </c>
-      <c r="G14">
-        <v>0.93177812969999985</v>
-      </c>
-      <c r="H14">
-        <v>0.92246034840299984</v>
-      </c>
-      <c r="I14">
-        <v>0.91323574491896986</v>
-      </c>
-      <c r="J14">
-        <v>0.90410338746978014</v>
-      </c>
-      <c r="K14">
-        <v>0.89506235359508235</v>
-      </c>
-      <c r="L14">
-        <v>0.88611173005913157</v>
-      </c>
-      <c r="M14">
-        <v>0.87725061275854022</v>
-      </c>
-      <c r="N14">
-        <v>0.86847810663095482</v>
-      </c>
-      <c r="O14">
-        <v>0.85979332556464527</v>
-      </c>
-      <c r="P14">
-        <v>0.85119539230899877</v>
-      </c>
-      <c r="Q14">
-        <v>0.84268343838590876</v>
-      </c>
-      <c r="R14">
-        <v>0.83425660400204971</v>
-      </c>
-      <c r="S14">
-        <v>0.82591403796202922</v>
-      </c>
-      <c r="T14">
-        <v>0.81765489758240895</v>
-      </c>
-      <c r="U14">
-        <v>0.80947834860658485</v>
-      </c>
-      <c r="V14">
-        <v>0.801383565120519</v>
-      </c>
-      <c r="W14">
-        <v>0.79336972946931383</v>
-      </c>
-      <c r="X14">
-        <v>0.78543603217462066</v>
-      </c>
-      <c r="Y14">
-        <v>0.77758167185287441</v>
-      </c>
-      <c r="Z14">
-        <v>0.76980585513434563</v>
-      </c>
-      <c r="AA14">
-        <v>0.76210779658300221</v>
-      </c>
-      <c r="AB14">
-        <v>0.7544867186171722</v>
-      </c>
-      <c r="AC14">
-        <v>0.74694185143100045</v>
-      </c>
-      <c r="AD14">
-        <v>0.7394724329166904</v>
-      </c>
-      <c r="AE14">
-        <v>0.73207770858752352</v>
-      </c>
-      <c r="AF14">
-        <v>0.72475693150164833</v>
-      </c>
-      <c r="AG14">
-        <v>0.71750936218663186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>0.97</v>
-      </c>
-      <c r="D15">
-        <v>0.9506</v>
-      </c>
-      <c r="E15">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F15">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G15">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H15">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I15">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J15">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K15">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L15">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M15">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N15">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O15">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P15">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q15">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R15">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S15">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T15">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U15">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V15">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W15">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X15">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y15">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z15">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA15">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB15">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC15">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD15">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE15">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF15">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG15">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>0.97</v>
-      </c>
-      <c r="D16">
-        <v>0.95545000000000002</v>
-      </c>
-      <c r="E16">
-        <v>0.94111825000000005</v>
-      </c>
-      <c r="F16">
-        <v>0.92700147625000007</v>
-      </c>
-      <c r="G16">
-        <v>0.91309645410625007</v>
-      </c>
-      <c r="H16">
-        <v>0.8994000072946563</v>
-      </c>
-      <c r="I16">
-        <v>0.88590900718523646</v>
-      </c>
-      <c r="J16">
-        <v>0.87262037207745791</v>
-      </c>
-      <c r="K16">
-        <v>0.85953106649629607</v>
-      </c>
-      <c r="L16">
-        <v>0.84663810049885158</v>
-      </c>
-      <c r="M16">
-        <v>0.83393852899136878</v>
-      </c>
-      <c r="N16">
-        <v>0.82142945105649823</v>
-      </c>
-      <c r="O16">
-        <v>0.80910800929065074</v>
-      </c>
-      <c r="P16">
-        <v>0.79697138915129095</v>
-      </c>
-      <c r="Q16">
-        <v>0.78501681831402159</v>
-      </c>
-      <c r="R16">
-        <v>0.77324156603931127</v>
-      </c>
-      <c r="S16">
-        <v>0.76164294254872156</v>
-      </c>
-      <c r="T16">
-        <v>0.7502182984104907</v>
-      </c>
-      <c r="U16">
-        <v>0.73896502393433339</v>
-      </c>
-      <c r="V16">
-        <v>0.72788054857531836</v>
-      </c>
-      <c r="W16">
-        <v>0.7169623403466886</v>
-      </c>
-      <c r="X16">
-        <v>0.70620790524148824</v>
-      </c>
-      <c r="Y16">
-        <v>0.69561478666286591</v>
-      </c>
-      <c r="Z16">
-        <v>0.68518056486292289</v>
-      </c>
-      <c r="AA16">
-        <v>0.67490285638997904</v>
-      </c>
-      <c r="AB16">
-        <v>0.66477931354412934</v>
-      </c>
-      <c r="AC16">
-        <v>0.65480762384096736</v>
-      </c>
-      <c r="AD16">
-        <v>0.64498550948335287</v>
-      </c>
-      <c r="AE16">
-        <v>0.63531072684110257</v>
-      </c>
-      <c r="AF16">
-        <v>0.62578106593848604</v>
-      </c>
-      <c r="AG16">
-        <v>0.61639434994940878</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>0.97</v>
-      </c>
-      <c r="D17">
-        <v>0.9506</v>
-      </c>
-      <c r="E17">
-        <v>0.93158799999999997</v>
-      </c>
-      <c r="F17">
-        <v>0.91295623999999997</v>
-      </c>
-      <c r="G17">
-        <v>0.89469711519999995</v>
-      </c>
-      <c r="H17">
-        <v>0.87680317289599996</v>
-      </c>
-      <c r="I17">
-        <v>0.85926710943807993</v>
-      </c>
-      <c r="J17">
-        <v>0.84208176724931838</v>
-      </c>
-      <c r="K17">
-        <v>0.82524013190433199</v>
-      </c>
-      <c r="L17">
-        <v>0.80873532926624536</v>
-      </c>
-      <c r="M17">
-        <v>0.79256062268092042</v>
-      </c>
-      <c r="N17">
-        <v>0.776709410227302</v>
-      </c>
-      <c r="O17">
-        <v>0.761175222022756</v>
-      </c>
-      <c r="P17">
-        <v>0.74595171758230083</v>
-      </c>
-      <c r="Q17">
-        <v>0.73103268323065485</v>
-      </c>
-      <c r="R17">
-        <v>0.71641202956604177</v>
-      </c>
-      <c r="S17">
-        <v>0.7020837889747209</v>
-      </c>
-      <c r="T17">
-        <v>0.68804211319522646</v>
-      </c>
-      <c r="U17">
-        <v>0.67428127093132195</v>
-      </c>
-      <c r="V17">
-        <v>0.66079564551269554</v>
-      </c>
-      <c r="W17">
-        <v>0.64757973260244162</v>
-      </c>
-      <c r="X17">
-        <v>0.63462813795039275</v>
-      </c>
-      <c r="Y17">
-        <v>0.62193557519138487</v>
-      </c>
-      <c r="Z17">
-        <v>0.60949686368755718</v>
-      </c>
-      <c r="AA17">
-        <v>0.59730692641380601</v>
-      </c>
-      <c r="AB17">
-        <v>0.58536078788552992</v>
-      </c>
-      <c r="AC17">
-        <v>0.57365357212781931</v>
-      </c>
-      <c r="AD17">
-        <v>0.56218050068526293</v>
-      </c>
-      <c r="AE17">
-        <v>0.55093689067155771</v>
-      </c>
-      <c r="AF17">
-        <v>0.53991815285812661</v>
-      </c>
-      <c r="AG17">
-        <v>0.52911978980096408</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>0.97</v>
-      </c>
-      <c r="D18">
-        <v>0.94574999999999998</v>
-      </c>
-      <c r="E18">
-        <v>0.92210625000000002</v>
-      </c>
-      <c r="F18">
-        <v>0.89905359375000005</v>
-      </c>
-      <c r="G18">
-        <v>0.87657725390625008</v>
-      </c>
-      <c r="H18">
-        <v>0.85466282255859383</v>
-      </c>
-      <c r="I18">
-        <v>0.83329625199462898</v>
-      </c>
-      <c r="J18">
-        <v>0.81246384569476326</v>
-      </c>
-      <c r="K18">
-        <v>0.79215224955239416</v>
-      </c>
-      <c r="L18">
-        <v>0.77234844331358432</v>
-      </c>
-      <c r="M18">
-        <v>0.75303973223074472</v>
-      </c>
-      <c r="N18">
-        <v>0.7342137389249761</v>
-      </c>
-      <c r="O18">
-        <v>0.7158583954518517</v>
-      </c>
-      <c r="P18">
-        <v>0.69796193556555541</v>
-      </c>
-      <c r="Q18">
-        <v>0.68051288717641656</v>
-      </c>
-      <c r="R18">
-        <v>0.6635000649970062</v>
-      </c>
-      <c r="S18">
-        <v>0.64691256337208103</v>
-      </c>
-      <c r="T18">
-        <v>0.63073974928777898</v>
-      </c>
-      <c r="U18">
-        <v>0.61497125555558452</v>
-      </c>
-      <c r="V18">
-        <v>0.59959697416669488</v>
-      </c>
-      <c r="W18">
-        <v>0.58460704981252753</v>
-      </c>
-      <c r="X18">
-        <v>0.56999187356721437</v>
-      </c>
-      <c r="Y18">
-        <v>0.555742076728034</v>
-      </c>
-      <c r="Z18">
-        <v>0.54184852480983314</v>
-      </c>
-      <c r="AA18">
-        <v>0.5283023116895873</v>
-      </c>
-      <c r="AB18">
-        <v>0.5150947538973476</v>
-      </c>
-      <c r="AC18">
-        <v>0.50221738504991387</v>
-      </c>
-      <c r="AD18">
-        <v>0.489661950423666</v>
-      </c>
-      <c r="AE18">
-        <v>0.47742040166307437</v>
-      </c>
-      <c r="AF18">
-        <v>0.46548489162149753</v>
-      </c>
-      <c r="AG18">
-        <v>0.4538477693309601</v>
+        <v>0.73230336965439757</v>
       </c>
     </row>
   </sheetData>
